--- a/tests/criterio-cfo/material/control-ec/finanzas/1790000001001-comercial-control/2026-09/20-bancos/pacifico-6702/extracto.xlsx
+++ b/tests/criterio-cfo/material/control-ec/finanzas/1790000001001-comercial-control/2026-09/20-bancos/pacifico-6702/extracto.xlsx
@@ -62,6 +62,11 @@
           <t>saldo</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>moneda</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -82,6 +87,11 @@
       </c>
       <c r="E2">
         <v>75000.00</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -104,6 +114,11 @@
       <c r="E3">
         <v>45000.00</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
